--- a/excel-data/dish.xlsx
+++ b/excel-data/dish.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyCreation\Web\mogumogu-pick\excel-data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AF5F02A-6647-4AFC-8C7F-E7914E1FE976}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC8B3229-441C-4F02-B1E1-AB7EFB0745DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{2C4057A3-4DF4-41B5-A441-0D94A14DFD1E}"/>
   </bookViews>
   <sheets>
-    <sheet name="工作表1" sheetId="1" r:id="rId1"/>
+    <sheet name="dish" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
